--- a/GREENBANK0_301A/project/Summary.xlsx
+++ b/GREENBANK0_301A/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="499">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -160,7 +160,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -1536,6 +1539,9 @@
   </si>
   <si>
     <t>amux2</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -1906,47 +1912,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -1956,52 +1962,52 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2016,7 +2022,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2036,7 +2042,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2051,7 +2057,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +2072,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2086,12 +2092,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2106,212 +2112,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2326,12 +2332,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2346,7 +2352,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2366,127 +2372,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2501,7 +2507,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2766,17 +2772,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +2797,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2811,17 +2817,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2836,52 +2842,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2896,81 +2902,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" t="s">
         <v>193</v>
-      </c>
-      <c r="B6" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" t="s">
         <v>196</v>
-      </c>
-      <c r="B8" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" t="s">
         <v>201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2978,185 +2984,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3164,453 +3170,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B83" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B95" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B97" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B98" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B99" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3618,628 +3624,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B112" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B116" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B118" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B124" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B125" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B126" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B127" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B128" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B129" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B131" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B132" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B133" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B134" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B135" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B136" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B137" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B138" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B139" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B140" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B141" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B143" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B144" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B146" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B149" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B150" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B151" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B154" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B157" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B158" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B160" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B161" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B162" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B163" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B165" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B166" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B167" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B168" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B169" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B170" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B171" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B172" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B173" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B174" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B176" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B179" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B180" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4254,47 +4260,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4302,15 +4308,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4318,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -4333,246 +4339,246 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F5" t="s">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" t="s">
         <v>445</v>
       </c>
-      <c r="C6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" t="s">
-        <v>444</v>
-      </c>
       <c r="E6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F6" t="s">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F7" t="s">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F8" t="s">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F9" t="s">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F10" t="s">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F12" t="s">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F13" t="s">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="B14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F14" t="s">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="B15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E15" t="s">
         <v>1</v>
@@ -4581,18 +4587,18 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="B16" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D16" t="s">
         <v>458</v>
-      </c>
-      <c r="D16" t="s">
-        <v>457</v>
       </c>
       <c r="E16" t="s">
         <v>1</v>
@@ -4601,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4616,26 +4622,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4645,12 +4651,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4660,226 +4666,234 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B24" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B26" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B27" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B28" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B29" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B31" t="s">
-        <v>433</v>
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>498</v>
+      </c>
+      <c r="B32" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -4889,7 +4903,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4905,6 +4919,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4919,7 +4938,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4929,57 +4948,57 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -4989,7 +5008,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -4999,7 +5018,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -5009,57 +5028,57 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5074,7 +5093,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5084,7 +5103,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5099,7 +5118,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5109,7 +5128,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5124,7 +5143,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5134,47 +5153,47 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -5184,52 +5203,52 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -5244,37 +5263,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -5289,37 +5308,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Summary.xlsx
+++ b/GREENBANK0_301A/project/Summary.xlsx
@@ -32,16 +32,15 @@
     <sheet name="Project Summary" sheetId="23" r:id="rId23"/>
     <sheet name="Design Params and Codes" sheetId="24" r:id="rId24"/>
     <sheet name="DRM Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Register Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="DFT Summary" sheetId="27" r:id="rId27"/>
-    <sheet name="Nesto Usage Report" sheetId="28" r:id="rId28"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="455">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -160,175 +159,103 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+    <t>All symbols have nets.</t>
+  </si>
+  <si>
+    <t>Shorted Inputs</t>
+  </si>
+  <si>
+    <t>No Shorted Input Nets found.</t>
+  </si>
+  <si>
+    <t>Shorted Outputs</t>
+  </si>
+  <si>
+    <t>No Shorted Output Nets found.</t>
+  </si>
+  <si>
+    <t>Floating Inputs</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XU1</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.scli(scli)</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
+  </si>
+  <si>
+    <t>No Connects - Outputs</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE</t>
+  </si>
+  <si>
+    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>No Connects - Inputs</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
   </si>
   <si>
-    <t>XU9,SIMPV</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDlow</t>
-  </si>
-  <si>
-    <t>XU1,SIMPV</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPFIXEDmedium</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENhigh</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENlow</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU20,XAMPOPENmedium</t>
-  </si>
-  <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
-  </si>
-  <si>
-    <t>Floating Inputs</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(30)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(29)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDO1.factory_ldooutput(28)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOCONFIGURE1.enable_ldo(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOFIXED.enable_ldo(114)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOSTANDALONE.enable_ldo(116)</t>
-  </si>
-  <si>
-    <t>Floating pin XLDOUNITY.enable_ldo(119)</t>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>XU1,XceleraRING</t>
   </si>
   <si>
-    <t>Floating pin XCELINA.ten_taext(ten_taext)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.ten_tdext(ten_tdext)</t>
-  </si>
-  <si>
-    <t>XU1</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.scli(scli)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE</t>
-  </si>
-  <si>
-    <t>Floating pin XSERVICE.CELBG83021(CELBG83021)</t>
-  </si>
-  <si>
-    <t>Floating pin XCELIND.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "tdext", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>114 - {"path": "XU1,XceleraCORE,XU19,XLDOFIXED", "instance": "XLDOFIXED", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>116 - {"path": "XU1,XceleraCORE,XU19,XLDOSTANDALONE", "instance": "XLDOSTANDALONE", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XU1,XceleraCORE,XU19,XLDOUNITY", "instance": "XLDOUNITY", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_tdext - {"path": "XU1,XceleraRING,XCELIND", "instance": "XCELIND", "symbol": "ten_tdext", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -773,7 +700,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/sim_GREENBANK_301A.net</t>
+    <t>/tmp/kyle/mnt/celera/projects/Simplis/playrelease/Release/play301a/Regression/SIMPLIS_Data/sim_GREENBANK_301A.net</t>
   </si>
   <si>
     <t>gen_reports</t>
@@ -1364,70 +1291,10 @@
     <t>61</t>
   </si>
   <si>
-    <t>Register Summary</t>
+    <t>DFT Summary</t>
   </si>
   <si>
     <t>TMA</t>
-  </si>
-  <si>
-    <t>Bits</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>AMPCONTROLHIGHgain</t>
-  </si>
-  <si>
-    <t>rw</t>
-  </si>
-  <si>
-    <t>AMPCONTROLMEDIUMgain</t>
-  </si>
-  <si>
-    <t>AMPCONTROLSLOWgain</t>
-  </si>
-  <si>
-    <t>AMPLIFIERconfiguration</t>
-  </si>
-  <si>
-    <t>LDOconfigurationA</t>
-  </si>
-  <si>
-    <t>REF2output</t>
-  </si>
-  <si>
-    <t>REF3output</t>
-  </si>
-  <si>
-    <t>REFERENCEselect</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>SERVICEconfiguration</t>
-  </si>
-  <si>
-    <t>0x21</t>
-  </si>
-  <si>
-    <t>XU2</t>
-  </si>
-  <si>
-    <t>0x22</t>
-  </si>
-  <si>
-    <t>ro</t>
-  </si>
-  <si>
-    <t>0x23</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
   </si>
   <si>
     <t>Nesto Usage Report</t>
@@ -1907,52 +1774,52 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -1962,52 +1829,47 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>71</v>
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2022,7 +1884,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2042,7 +1904,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2057,7 +1919,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2072,7 +1934,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2092,12 +1954,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2112,212 +1974,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2332,12 +2194,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2214,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2372,127 +2234,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2507,7 +2369,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2772,17 +2634,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2797,7 +2659,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2817,17 +2679,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2842,52 +2704,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2902,81 +2764,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2984,185 +2846,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B33" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3170,453 +3032,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B67" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B69" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="B70" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B80" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B81" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="B87" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="B88" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B90" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="B95" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="B97" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B98" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3624,628 +3486,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="B103" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="B106" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="B107" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="B108" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="B109" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="B110" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="B112" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="B113" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="B117" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B118" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="B119" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B120" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="B121" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="B122" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B123" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="B124" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="B125" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B126" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="B127" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B128" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="B129" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="B130" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B131" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B132" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B133" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="B135" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="B136" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="B137" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B138" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="B139" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B140" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="B141" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B142" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B143" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="B144" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B145" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="B146" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B147" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B148" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B149" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B150" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B153" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B154" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B155" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B156" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B157" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="B158" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="B159" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B160" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B161" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="B162" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="B163" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B164" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="B165" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B166" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="B167" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="B168" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B169" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="B171" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="B172" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B173" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B174" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="B175" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="B176" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="B177" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="B178" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="B179" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="B180" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4260,47 +4122,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4308,15 +4170,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4324,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -4334,280 +4196,31 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" t="s">
-        <v>445</v>
-      </c>
-      <c r="E6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
-        <v>448</v>
-      </c>
-      <c r="C8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" t="s">
-        <v>445</v>
-      </c>
-      <c r="E8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" t="s">
-        <v>449</v>
-      </c>
-      <c r="C9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" t="s">
-        <v>445</v>
-      </c>
-      <c r="E9" t="s">
-        <v>433</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" t="s">
-        <v>449</v>
-      </c>
-      <c r="C10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>445</v>
-      </c>
-      <c r="E10" t="s">
-        <v>433</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" t="s">
-        <v>450</v>
-      </c>
-      <c r="C11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" t="s">
-        <v>445</v>
-      </c>
-      <c r="E11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" t="s">
-        <v>451</v>
-      </c>
-      <c r="C12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D12" t="s">
-        <v>445</v>
-      </c>
-      <c r="E12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="B13" t="s">
-        <v>452</v>
-      </c>
-      <c r="C13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D13" t="s">
-        <v>445</v>
-      </c>
-      <c r="E13" t="s">
-        <v>311</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" t="s">
-        <v>454</v>
-      </c>
-      <c r="C14" t="s">
-        <v>455</v>
-      </c>
-      <c r="D14" t="s">
-        <v>445</v>
-      </c>
-      <c r="E14" t="s">
-        <v>227</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" t="s">
-        <v>456</v>
-      </c>
-      <c r="C15" t="s">
-        <v>457</v>
-      </c>
-      <c r="D15" t="s">
-        <v>458</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" t="s">
-        <v>456</v>
-      </c>
-      <c r="C16" t="s">
-        <v>459</v>
-      </c>
-      <c r="D16" t="s">
-        <v>458</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>239</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4617,46 +4230,12 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4666,234 +4245,234 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="B5" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="B6" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
-        <v>473</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="B10" t="s">
-        <v>475</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="B11" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="B12" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="B15" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="B16" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>488</v>
+        <v>444</v>
       </c>
       <c r="B22" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
       <c r="B23" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>490</v>
+        <v>446</v>
       </c>
       <c r="B24" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="B26" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="B27" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c r="B29" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="B30" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
       <c r="B31" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="B32" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4903,7 +4482,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4919,11 +4498,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4933,12 +4507,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4948,137 +4522,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -5093,7 +4537,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5103,7 +4547,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5118,7 +4562,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5128,7 +4572,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5138,12 +4582,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5153,102 +4597,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5258,42 +4622,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -5303,42 +4647,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Summary.xlsx
+++ b/GREENBANK0_301A/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="478">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -216,30 +216,6 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
-  </si>
-  <si>
-    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
@@ -256,6 +232,9 @@
   </si>
   <si>
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>tmi - {"path": "XU1,XceleraCORE", "instance": "XceleraCORE", "symbol": "tmi", "io": "inout", "bus": "[4:0]", "type": "child"}</t>
   </si>
   <si>
     <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
@@ -493,21 +472,57 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 18, 'efficiency': '71.9%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 17, 'efficiency': '73.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 5, 'efficiency': '68.8%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
+  </si>
+  <si>
+    <t>{'name': 'drm32', 'bits': 32, 'noconns': 8, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
+  </si>
+  <si>
+    <t>{'name': 'drm32', 'bits': 32, 'noconns': 11, 'efficiency': '65.6%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE20mA</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>{'cells': 9, 'bytes': 42.0, 'noconns': 100, 'efficiency': '70.2%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
     <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
@@ -1279,6 +1294,54 @@
     <t>1</t>
   </si>
   <si>
+    <t>drm_hex0x01</t>
+  </si>
+  <si>
+    <t>drm64</t>
+  </si>
+  <si>
+    <t>drm_hex0x02</t>
+  </si>
+  <si>
+    <t>drm_hex0x03</t>
+  </si>
+  <si>
+    <t>drm16</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>drm_hex0x04</t>
+  </si>
+  <si>
+    <t>drm32</t>
+  </si>
+  <si>
+    <t>drm_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>drm_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>drm_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>drm_hex0x08</t>
+  </si>
+  <si>
+    <t>drm_hex0x09</t>
+  </si>
+  <si>
     <t>DRM to Memory Check</t>
   </si>
   <si>
@@ -1288,6 +1351,9 @@
     <t>Allowed &lt;= 61</t>
   </si>
   <si>
+    <t>51.0</t>
+  </si>
+  <si>
     <t>61</t>
   </si>
   <si>
@@ -1312,34 +1378,34 @@
     <t>238</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>inv</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>nand2</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>PEBBLEtielo</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>18</t>
   </si>
   <si>
     <t>switchgnd</t>
@@ -1351,6 +1417,12 @@
     <t>datamap0</t>
   </si>
   <si>
+    <t>drmmodule</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>amplifier</t>
   </si>
   <si>
@@ -1406,9 +1478,6 @@
   </si>
   <si>
     <t>amux2</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -1774,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1784,92 +1853,57 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1884,7 +1918,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1904,7 +1938,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1919,7 +1953,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1968,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1954,12 +1988,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1974,212 +2008,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2194,12 +2228,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2214,7 +2248,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2234,127 +2268,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2364,17 +2398,92 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2634,17 +2743,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +2768,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2679,17 +2788,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2704,52 +2813,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2764,81 +2873,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2846,185 +2955,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3032,453 +3141,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B55" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B67" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B68" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B69" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B70" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B80" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B90" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B94" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B96" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3486,628 +3595,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B102" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B106" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B107" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B108" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B109" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B110" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B111" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B112" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B113" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B116" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B117" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B118" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B119" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B120" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B121" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B122" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
+        <v>318</v>
+      </c>
+      <c r="B123" t="s">
         <v>313</v>
-      </c>
-      <c r="B123" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B125" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B126" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B127" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B128" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B129" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B130" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B131" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B132" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B133" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B137" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B138" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B139" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B140" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B141" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B142" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B143" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B144" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B146" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B149" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B150" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B151" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B152" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B153" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B154" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B155" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B156" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B157" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B158" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B159" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B160" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B161" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B162" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B163" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B164" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B165" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B166" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B167" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B168" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B169" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B170" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B171" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B172" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B173" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B174" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B175" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B176" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B177" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B178" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B179" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B180" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4117,76 +4226,418 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>411</v>
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" t="s">
+        <v>182</v>
+      </c>
+      <c r="I5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J5" t="s">
+        <v>326</v>
+      </c>
+      <c r="K5" t="s">
+        <v>182</v>
+      </c>
+      <c r="L5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>413</v>
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" t="s">
+        <v>326</v>
+      </c>
+      <c r="J6" t="s">
+        <v>326</v>
+      </c>
+      <c r="K6" t="s">
+        <v>182</v>
+      </c>
+      <c r="L6" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>419</v>
+      </c>
+      <c r="C7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G7" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" t="s">
+        <v>421</v>
+      </c>
+      <c r="I7" t="s">
+        <v>421</v>
+      </c>
+      <c r="J7" t="s">
+        <v>421</v>
+      </c>
+      <c r="K7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E8" t="s">
+        <v>421</v>
+      </c>
+      <c r="F8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H8" t="s">
+        <v>421</v>
+      </c>
+      <c r="I8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K8" t="s">
+        <v>182</v>
+      </c>
+      <c r="L8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E9" t="s">
+        <v>421</v>
+      </c>
+      <c r="F9" t="s">
+        <v>421</v>
+      </c>
+      <c r="G9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H9" t="s">
+        <v>421</v>
+      </c>
+      <c r="I9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J9" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" t="s">
+        <v>182</v>
+      </c>
+      <c r="L9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" t="s">
+        <v>421</v>
+      </c>
+      <c r="G10" t="s">
+        <v>421</v>
+      </c>
+      <c r="H10" t="s">
+        <v>421</v>
+      </c>
+      <c r="I10" t="s">
+        <v>182</v>
+      </c>
+      <c r="J10" t="s">
+        <v>182</v>
+      </c>
+      <c r="K10" t="s">
+        <v>182</v>
+      </c>
+      <c r="L10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" t="s">
+        <v>428</v>
+      </c>
+      <c r="C11" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" t="s">
+        <v>421</v>
+      </c>
+      <c r="F11" t="s">
+        <v>421</v>
+      </c>
+      <c r="G11" t="s">
+        <v>421</v>
+      </c>
+      <c r="H11" t="s">
+        <v>421</v>
+      </c>
+      <c r="I11" t="s">
+        <v>182</v>
+      </c>
+      <c r="J11" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" t="s">
+        <v>421</v>
+      </c>
+      <c r="F12" t="s">
+        <v>421</v>
+      </c>
+      <c r="G12" t="s">
+        <v>421</v>
+      </c>
+      <c r="H12" t="s">
+        <v>421</v>
+      </c>
+      <c r="I12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" t="s">
+        <v>182</v>
+      </c>
+      <c r="L12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" t="s">
+        <v>431</v>
+      </c>
+      <c r="C13" t="s">
+        <v>396</v>
+      </c>
+      <c r="D13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" t="s">
+        <v>421</v>
+      </c>
+      <c r="F13" t="s">
+        <v>421</v>
+      </c>
+      <c r="G13" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" t="s">
+        <v>421</v>
+      </c>
+      <c r="I13" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" t="s">
+        <v>182</v>
+      </c>
+      <c r="K13" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -4201,26 +4652,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -4235,7 +4686,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4245,234 +4696,234 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="B8" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="B9" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="B10" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B11" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="B15" t="s">
-        <v>409</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="B22" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="B23" t="s">
-        <v>410</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="B24" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="B25" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="B26" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="B27" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="B28" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="B29" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="B30" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="B31" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="B32" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Summary.xlsx
+++ b/GREENBANK0_301A/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="528">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -105,6 +105,9 @@
     <t>Xdatamap4 (datamap.code) missing expected field datamap_code_2</t>
   </si>
   <si>
+    <t>XUSERVICEreference dftprobe_description total_bits:3 cannot be 'text'</t>
+  </si>
+  <si>
     <t>XU1,XceleraCORE,XU19</t>
   </si>
   <si>
@@ -195,6 +198,9 @@
     <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
   </si>
   <si>
+    <t>Floating pin XceleraRING.unlock(unlock)</t>
+  </si>
+  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -241,6 +247,9 @@
   </si>
   <si>
     <t>sdai - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdai", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>unlock - {"path": "XU1,XceleraRING", "instance": "XceleraRING", "symbol": "unlock", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -517,10 +526,49 @@
     <t>DFT Efficiency</t>
   </si>
   <si>
+    <t>XU1,XceleraCORE,XSERVICE,XBYPASS</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8a', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOconfigNO1</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPFIXEDlow</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPFIXEDmedium</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENhigh</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENlow</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU20,XAMPOPENmedium</t>
+  </si>
+  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 24, 'bytes': 24.0, 'noconns': 119, 'efficiency': '38.0%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -529,7 +577,7 @@
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 3</t>
+    <t>needed: 5</t>
   </si>
   <si>
     <t>spares: 14</t>
@@ -568,18 +616,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
     <t>dft_ignore_bricks</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1363,6 +1411,99 @@
     <t>TMA</t>
   </si>
   <si>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8a</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
     <t>Nesto Usage Report</t>
   </si>
   <si>
@@ -1381,7 +1522,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>111</t>
+    <t>189</t>
   </si>
   <si>
     <t>inv</t>
@@ -1396,18 +1537,21 @@
     <t>35</t>
   </si>
   <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>dftprobeModel0</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>dbuf</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>switchgnd</t>
   </si>
   <si>
@@ -1429,6 +1573,9 @@
     <t>IPOTTldo</t>
   </si>
   <si>
+    <t>dftprobeModel2</t>
+  </si>
+  <si>
     <t>reference</t>
   </si>
   <si>
@@ -1466,6 +1613,9 @@
   </si>
   <si>
     <t>nand3</t>
+  </si>
+  <si>
+    <t>dftprobeModel3</t>
   </si>
   <si>
     <t>delayfixed</t>
@@ -1843,67 +1993,72 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1918,7 +2073,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1938,7 +2093,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1953,7 +2108,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +2123,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1988,12 +2143,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2008,212 +2163,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2228,12 +2383,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2248,7 +2403,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2268,127 +2423,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2558,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2413,77 +2568,77 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2648,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2582,12 +2737,12 @@
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2627,73 +2782,73 @@
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>6</v>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>6</v>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>6</v>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>22</v>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -2713,7 +2868,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -2729,6 +2884,11 @@
     <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2743,17 +2903,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2763,17 +2923,232 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2788,17 +3163,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2813,52 +3188,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2873,81 +3248,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2955,185 +3330,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" t="s">
         <v>192</v>
-      </c>
-      <c r="B21" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3141,453 +3516,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B68" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B69" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B70" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B81" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B84" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B90" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B94" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3595,628 +3970,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B102" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B103" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B106" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B107" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B108" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="B109" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B110" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B111" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B112" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="B113" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="B116" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B117" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B118" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B119" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B120" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B121" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B122" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B123" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B124" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B125" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B126" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B127" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B128" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B129" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="B130" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B132" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="B133" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B134" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="B135" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B136" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="B137" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="B138" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B139" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B140" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="B141" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B142" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B143" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B144" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B145" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="B146" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B147" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="B149" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="B150" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B151" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="B152" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B153" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="B154" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="B155" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="B156" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B157" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B158" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="B159" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B160" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B161" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B162" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B163" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="B164" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B165" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="B166" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="B167" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="B168" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="B169" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="B170" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="B171" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="B172" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="B173" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B174" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="B175" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B176" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="B177" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="B178" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="B179" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="B180" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4231,47 +4606,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4282,37 +4657,37 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="D5" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="E5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="F5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="G5" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="H5" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="I5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="J5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="K5" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L5" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -4320,37 +4695,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="D6" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="E6" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="I6" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="J6" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="K6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L6" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4358,286 +4733,286 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C7" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="E7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="J7" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="K7" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L7" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E8" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F8" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G8" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H8" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I8" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K8" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L8" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="D9" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E9" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F9" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G9" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H9" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I9" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L9" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="D10" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E10" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F10" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G10" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H10" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L10" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="C11" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="D11" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E11" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F11" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G11" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H11" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L11" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C12" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="D12" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E12" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F12" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G12" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H12" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I12" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K12" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L12" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C13" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="D13" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E13" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="G13" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H13" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I13" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K13" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="L13" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B16" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -4647,31 +5022,367 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" t="s">
+        <v>443</v>
+      </c>
+      <c r="D10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" t="s">
+        <v>464</v>
+      </c>
+      <c r="C11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" t="s">
         <v>410</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="D12" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" t="s">
         <v>412</v>
+      </c>
+      <c r="D13" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s">
+        <v>467</v>
+      </c>
+      <c r="C14" t="s">
+        <v>414</v>
+      </c>
+      <c r="D14" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C15" t="s">
+        <v>469</v>
+      </c>
+      <c r="D15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" t="s">
+        <v>357</v>
+      </c>
+      <c r="D16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" t="s">
+        <v>471</v>
+      </c>
+      <c r="C17" t="s">
+        <v>472</v>
+      </c>
+      <c r="D17" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" t="s">
+        <v>473</v>
+      </c>
+      <c r="C18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>475</v>
+      </c>
+      <c r="C19" t="s">
+        <v>290</v>
+      </c>
+      <c r="D19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>477</v>
+      </c>
+      <c r="C20" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>478</v>
+      </c>
+      <c r="C21" t="s">
+        <v>331</v>
+      </c>
+      <c r="D21" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>479</v>
+      </c>
+      <c r="C22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" t="s">
+        <v>480</v>
+      </c>
+      <c r="C23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" t="s">
+        <v>340</v>
+      </c>
+      <c r="D24" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" t="s">
+        <v>482</v>
+      </c>
+      <c r="C25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" t="s">
+        <v>483</v>
+      </c>
+      <c r="C26" t="s">
+        <v>344</v>
+      </c>
+      <c r="D26" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>484</v>
+      </c>
+      <c r="C27" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>485</v>
+      </c>
+      <c r="C28" t="s">
+        <v>369</v>
+      </c>
+      <c r="D28" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -4681,12 +5392,12 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4696,234 +5407,258 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>441</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>442</v>
+        <v>489</v>
       </c>
       <c r="B5" t="s">
-        <v>443</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>444</v>
+        <v>491</v>
       </c>
       <c r="B6" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="B8" t="s">
-        <v>449</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="B9" t="s">
-        <v>451</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>452</v>
+        <v>499</v>
       </c>
       <c r="B10" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
       <c r="B11" t="s">
-        <v>455</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="B12" t="s">
-        <v>302</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="B13" t="s">
-        <v>458</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>461</v>
+        <v>508</v>
       </c>
       <c r="B16" t="s">
-        <v>414</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>462</v>
+        <v>509</v>
       </c>
       <c r="B17" t="s">
-        <v>414</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="B19" t="s">
-        <v>292</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="B20" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>466</v>
+        <v>513</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>469</v>
+        <v>516</v>
       </c>
       <c r="B24" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>470</v>
+        <v>517</v>
       </c>
       <c r="B25" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>471</v>
+        <v>518</v>
       </c>
       <c r="B26" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="B28" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="B29" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>475</v>
+        <v>522</v>
       </c>
       <c r="B30" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>476</v>
+        <v>523</v>
       </c>
       <c r="B31" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="B32" t="s">
-        <v>415</v>
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>525</v>
+      </c>
+      <c r="B33" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>526</v>
+      </c>
+      <c r="B34" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>527</v>
+      </c>
+      <c r="B35" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4938,7 +5673,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4948,7 +5683,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4963,7 +5698,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4973,7 +5708,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4988,7 +5723,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4998,7 +5733,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5013,7 +5748,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5023,7 +5758,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5033,12 +5768,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5048,22 +5783,27 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -5078,17 +5818,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -5103,27 +5843,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Summary.xlsx
+++ b/GREENBANK0_301A/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="531">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -180,31 +180,26 @@
     <t>Shorted Outputs</t>
   </si>
   <si>
-    <t>No Shorted Output Nets found.</t>
+    <t xml:space="preserve">-------------------------------------------------- Shorted OUTPUTS (!!! MUST FIX !!! - not allowed) --------------------------------------------------
+</t>
+  </si>
+  <si>
+    <t>XU1</t>
+  </si>
+  <si>
+    <t>Shorted output PORB97836 XceleraREGISTER.PORB97836 --&gt; XceleraSERDES.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XU1</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.scli(scli)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraREGISTER.sdai(sdai)</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraRING.unlock(unlock)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XceleraREGISTER.sdapd_registermap(pd0)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
@@ -216,12 +211,63 @@
     <t>CELBG83021 - {"path": "XU1,XceleraCORE,XSERVICE", "instance": "XSERVICE", "symbol": "CELBG83021", "io": "output", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>pd0 - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdapd_registermap", "io": "output", "bus": "", "type": "child"}</t>
+    <t>XU1,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>scli - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "scli", "io": "output", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "scl_register", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_register - {"path": "XU1,XceleraSERDES,XSERDESinputSINGLEregister", "instance": "XSERDESinputSINGLEregister", "symbol": "sda_register", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
+  </si>
+  <si>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+  </si>
+  <si>
+    <t>30 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>29 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>28 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA,XLDO1", "instance": "XLDO1", "symbol": "factory_ldooutput", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
     <t>117 - {"path": "XU1,XceleraCORE,XU19,XLDOCONFIGURE1", "instance": "XLDOCONFIGURE1", "symbol": "enable_ldo", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
@@ -240,16 +286,43 @@
     <t>ten_taext - {"path": "XU1,XceleraRING,XCELINA", "instance": "XCELINA", "symbol": "ten_taext", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>tmi - {"path": "XU1,XceleraCORE", "instance": "XceleraCORE", "symbol": "tmi", "io": "inout", "bus": "[4:0]", "type": "child"}</t>
-  </si>
-  <si>
-    <t>scli - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "scli", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>sdai - {"path": "XU1,XceleraREGISTER", "instance": "XceleraREGISTER", "symbol": "sdai", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>unlock - {"path": "XU1,XceleraRING", "instance": "XceleraRING", "symbol": "unlock", "io": "input", "bus": "", "type": "child"}</t>
+    <t>sdai - {"path": "XU1,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "sdai", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_bistok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_bistok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_programdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XU1,XceleraSERDES,XSERDESdftYesYes", "instance": "XSERDESdftYesYes", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XU1,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -481,30 +554,42 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 18, 'efficiency': '71.9%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 17, 'efficiency': '73.4%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 5, 'efficiency': '68.8%'}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE1</t>
-  </si>
-  <si>
-    <t>{'name': 'drm32', 'bits': 32, 'noconns': 8, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOCONFIGURE20mA</t>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XSERVICE,XBYPASS</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8a', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOconfigNO1</t>
+  </si>
+  <si>
+    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19,XLDOFIXED1</t>
   </si>
   <si>
-    <t>{'name': 'drm32', 'bits': 32, 'noconns': 11, 'efficiency': '65.6%'}</t>
-  </si>
-  <si>
     <t>XU1,XceleraCORE,XU19,XLDOSTANDALONE</t>
   </si>
   <si>
@@ -514,39 +599,6 @@
     <t>XU1,XceleraCORE,XU19,XLDOUNITY</t>
   </si>
   <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 9, 'bytes': 42.0, 'noconns': 100, 'efficiency': '70.2%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XSERVICE,XBYPASS</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8a', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOconfigNO1</t>
-  </si>
-  <si>
-    <t>XU1,XceleraCORE,XU19,XLDOFIXED</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
@@ -1342,105 +1394,63 @@
     <t>1</t>
   </si>
   <si>
-    <t>drm_hex0x01</t>
-  </si>
-  <si>
-    <t>drm64</t>
-  </si>
-  <si>
-    <t>drm_hex0x02</t>
-  </si>
-  <si>
-    <t>drm_hex0x03</t>
-  </si>
-  <si>
-    <t>drm16</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>drm_hex0x04</t>
-  </si>
-  <si>
-    <t>drm32</t>
-  </si>
-  <si>
-    <t>drm_hex0x05</t>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
+  </si>
+  <si>
+    <t>TMA</t>
+  </si>
+  <si>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8a</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
   </si>
   <si>
     <t>0x05</t>
   </si>
   <si>
-    <t>drm_hex0x06</t>
+    <t>dft_hex0x06</t>
   </si>
   <si>
     <t>0x06</t>
   </si>
   <si>
-    <t>drm_hex0x07</t>
+    <t>dft_hex0x07</t>
   </si>
   <si>
     <t>0x07</t>
   </si>
   <si>
-    <t>drm_hex0x08</t>
-  </si>
-  <si>
-    <t>drm_hex0x09</t>
-  </si>
-  <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>dft_hex0x01</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x02</t>
-  </si>
-  <si>
-    <t>DFTtm8</t>
-  </si>
-  <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>DFTtm8a</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
     <t>dft_hex0x08</t>
   </si>
   <si>
@@ -1522,7 +1532,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>189</t>
+    <t>121</t>
   </si>
   <si>
     <t>inv</t>
@@ -1561,18 +1571,15 @@
     <t>datamap0</t>
   </si>
   <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>amplifier</t>
   </si>
   <si>
     <t>IPOTTldo</t>
   </si>
   <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
     <t>dftprobeModel2</t>
   </si>
   <si>
@@ -1628,6 +1635,9 @@
   </si>
   <si>
     <t>amux2</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
 </sst>
 </file>
@@ -1993,72 +2003,157 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>64</v>
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>66</v>
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2168,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2093,7 +2188,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2108,7 +2203,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2123,7 +2218,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2143,12 +2238,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2163,212 +2258,212 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2383,12 +2478,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2498,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2423,127 +2518,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2553,92 +2648,17 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>152</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2903,17 +2923,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2928,17 +2948,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -2948,107 +2968,107 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -3058,7 +3078,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -3068,7 +3088,7 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -3078,7 +3098,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -3088,57 +3108,57 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -3148,7 +3168,7 @@
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3163,17 +3183,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3188,52 +3208,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3248,81 +3268,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3330,185 +3350,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B34" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -3516,453 +3536,453 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B41" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B50" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B51" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="B52" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B57" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="B64" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B68" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B69" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="B70" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B81" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B82" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B84" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B85" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B86" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B87" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B88" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B90" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B94" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B96" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B97" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -3970,628 +3990,628 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="B103" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B106" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B107" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B108" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B109" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B110" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="B111" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B112" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B116" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B117" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B118" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B119" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B121" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B122" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B123" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B124" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B125" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="B126" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="B127" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B128" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B129" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="B130" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B131" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B132" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B133" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B134" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B135" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B136" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B137" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B138" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B142" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="B143" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B144" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B145" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B146" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B147" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="B148" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B149" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="B150" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B151" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="B152" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B153" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B154" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="B155" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B156" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="B157" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B158" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B159" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="B160" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="B161" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="B164" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="B166" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B167" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="B168" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B169" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B170" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B171" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="B172" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B173" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B174" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B175" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="B176" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="B177" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="B178" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="B179" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="B180" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4601,417 +4621,75 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>432</v>
-      </c>
-      <c r="C5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" t="s">
-        <v>433</v>
-      </c>
-      <c r="E5" t="s">
-        <v>342</v>
-      </c>
-      <c r="F5" t="s">
-        <v>342</v>
-      </c>
-      <c r="G5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" t="s">
-        <v>198</v>
-      </c>
-      <c r="I5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J5" t="s">
-        <v>342</v>
-      </c>
-      <c r="K5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L5" t="s">
-        <v>198</v>
+      <c r="A5" s="1" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" t="s">
-        <v>433</v>
-      </c>
-      <c r="E6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6" t="s">
-        <v>198</v>
-      </c>
-      <c r="H6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I6" t="s">
-        <v>342</v>
-      </c>
-      <c r="J6" t="s">
-        <v>342</v>
-      </c>
-      <c r="K6" t="s">
-        <v>198</v>
-      </c>
-      <c r="L6" t="s">
-        <v>198</v>
+      <c r="A6" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D7" t="s">
-        <v>436</v>
-      </c>
-      <c r="E7" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" t="s">
-        <v>437</v>
-      </c>
-      <c r="G7" t="s">
-        <v>437</v>
-      </c>
-      <c r="H7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I7" t="s">
-        <v>437</v>
-      </c>
-      <c r="J7" t="s">
-        <v>437</v>
-      </c>
-      <c r="K7" t="s">
-        <v>198</v>
-      </c>
-      <c r="L7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>438</v>
-      </c>
-      <c r="C8" t="s">
-        <v>408</v>
-      </c>
-      <c r="D8" t="s">
-        <v>439</v>
-      </c>
-      <c r="E8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F8" t="s">
-        <v>437</v>
-      </c>
-      <c r="G8" t="s">
-        <v>437</v>
-      </c>
-      <c r="H8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I8" t="s">
-        <v>198</v>
-      </c>
-      <c r="J8" t="s">
-        <v>198</v>
-      </c>
-      <c r="K8" t="s">
-        <v>198</v>
-      </c>
-      <c r="L8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" t="s">
-        <v>440</v>
-      </c>
-      <c r="C9" t="s">
-        <v>441</v>
-      </c>
-      <c r="D9" t="s">
-        <v>439</v>
-      </c>
-      <c r="E9" t="s">
-        <v>437</v>
-      </c>
-      <c r="F9" t="s">
-        <v>437</v>
-      </c>
-      <c r="G9" t="s">
-        <v>437</v>
-      </c>
-      <c r="H9" t="s">
-        <v>437</v>
-      </c>
-      <c r="I9" t="s">
-        <v>198</v>
-      </c>
-      <c r="J9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K9" t="s">
-        <v>198</v>
-      </c>
-      <c r="L9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" t="s">
-        <v>443</v>
-      </c>
-      <c r="D10" t="s">
-        <v>439</v>
-      </c>
-      <c r="E10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F10" t="s">
-        <v>437</v>
-      </c>
-      <c r="G10" t="s">
-        <v>437</v>
-      </c>
-      <c r="H10" t="s">
-        <v>437</v>
-      </c>
-      <c r="I10" t="s">
-        <v>198</v>
-      </c>
-      <c r="J10" t="s">
-        <v>198</v>
-      </c>
-      <c r="K10" t="s">
-        <v>198</v>
-      </c>
-      <c r="L10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B11" t="s">
-        <v>444</v>
-      </c>
-      <c r="C11" t="s">
-        <v>445</v>
-      </c>
-      <c r="D11" t="s">
-        <v>439</v>
-      </c>
-      <c r="E11" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" t="s">
-        <v>437</v>
-      </c>
-      <c r="G11" t="s">
-        <v>437</v>
-      </c>
-      <c r="H11" t="s">
-        <v>437</v>
-      </c>
-      <c r="I11" t="s">
-        <v>198</v>
-      </c>
-      <c r="J11" t="s">
-        <v>198</v>
-      </c>
-      <c r="K11" t="s">
-        <v>198</v>
-      </c>
-      <c r="L11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" t="s">
-        <v>446</v>
-      </c>
-      <c r="C12" t="s">
-        <v>410</v>
-      </c>
-      <c r="D12" t="s">
-        <v>439</v>
-      </c>
-      <c r="E12" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" t="s">
-        <v>437</v>
-      </c>
-      <c r="G12" t="s">
-        <v>437</v>
-      </c>
-      <c r="H12" t="s">
-        <v>437</v>
-      </c>
-      <c r="I12" t="s">
-        <v>198</v>
-      </c>
-      <c r="J12" t="s">
-        <v>198</v>
-      </c>
-      <c r="K12" t="s">
-        <v>198</v>
-      </c>
-      <c r="L12" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C13" t="s">
-        <v>412</v>
-      </c>
-      <c r="D13" t="s">
-        <v>439</v>
-      </c>
-      <c r="E13" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" t="s">
-        <v>437</v>
-      </c>
-      <c r="G13" t="s">
-        <v>437</v>
-      </c>
-      <c r="H13" t="s">
-        <v>437</v>
-      </c>
-      <c r="I13" t="s">
-        <v>198</v>
-      </c>
-      <c r="J13" t="s">
-        <v>198</v>
-      </c>
-      <c r="K13" t="s">
-        <v>198</v>
-      </c>
-      <c r="L13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>451</v>
-      </c>
-      <c r="B16" t="s">
         <v>452</v>
       </c>
     </row>
@@ -5032,32 +4710,32 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>454</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B5" t="s">
         <v>455</v>
       </c>
       <c r="C5" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
         <v>456</v>
@@ -5071,7 +4749,7 @@
         <v>457</v>
       </c>
       <c r="C6" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
         <v>458</v>
@@ -5085,7 +4763,7 @@
         <v>459</v>
       </c>
       <c r="C7" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D7" t="s">
         <v>460</v>
@@ -5099,7 +4777,7 @@
         <v>461</v>
       </c>
       <c r="C8" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="D8" t="s">
         <v>460</v>
@@ -5113,7 +4791,7 @@
         <v>462</v>
       </c>
       <c r="C9" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="D9" t="s">
         <v>460</v>
@@ -5124,10 +4802,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C10" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="D10" t="s">
         <v>456</v>
@@ -5135,13 +4813,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C11" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="D11" t="s">
         <v>456</v>
@@ -5149,13 +4827,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C12" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="D12" t="s">
         <v>456</v>
@@ -5163,13 +4841,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="D13" t="s">
         <v>456</v>
@@ -5177,13 +4855,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C14" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="D14" t="s">
         <v>456</v>
@@ -5191,13 +4869,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C15" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D15" t="s">
         <v>456</v>
@@ -5205,13 +4883,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C16" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D16" t="s">
         <v>456</v>
@@ -5219,13 +4897,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C17" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D17" t="s">
         <v>456</v>
@@ -5233,13 +4911,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C18" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D18" t="s">
         <v>456</v>
@@ -5250,13 +4928,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C19" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="D19" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5264,10 +4942,10 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C20" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D20" t="s">
         <v>456</v>
@@ -5278,10 +4956,10 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="D21" t="s">
         <v>456</v>
@@ -5292,10 +4970,10 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C22" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D22" t="s">
         <v>456</v>
@@ -5303,13 +4981,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="D23" t="s">
         <v>456</v>
@@ -5317,13 +4995,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C24" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="D24" t="s">
         <v>456</v>
@@ -5331,13 +5009,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C25" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="D25" t="s">
         <v>456</v>
@@ -5345,13 +5023,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B26" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C26" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="D26" t="s">
         <v>456</v>
@@ -5359,13 +5037,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C27" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="D27" t="s">
         <v>456</v>
@@ -5376,13 +5054,13 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C28" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="D28" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5392,12 +5070,12 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5407,258 +5085,266 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B7" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B9" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B10" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B11" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B12" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B14" t="s">
-        <v>506</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B18" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B19" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B20" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B21" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B25" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B26" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B27" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B28" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B30" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B31" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B32" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B33" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B34" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B35" t="s">
-        <v>431</v>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>530</v>
+      </c>
+      <c r="B36" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -5743,7 +5429,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5759,6 +5445,16 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -5768,12 +5464,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5783,27 +5479,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -5818,17 +5494,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -5838,32 +5514,72 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
